--- a/diseases/d126/2000-2004.xlsx
+++ b/diseases/d126/2000-2004.xlsx
@@ -2689,9 +2689,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2982,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3275,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3568,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3861,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4154,6 @@
       <c r="O25" t="n">
         <v>4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -4465,9 +4447,6 @@
       <c r="O27" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -4761,9 +4740,6 @@
       <c r="O29" t="n">
         <v>19</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.04038817886470444</v>
       </c>
@@ -5057,9 +5033,6 @@
       <c r="O31" t="n">
         <v>13</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.02763401711795567</v>
       </c>
@@ -5353,9 +5326,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5619,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -5945,9 +5912,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6241,9 +6205,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6537,9 +6498,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6833,9 +6791,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7129,9 +7084,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7425,9 +7377,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7670,6 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -8017,9 +7963,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -8313,9 +8256,6 @@
       <c r="O53" t="n">
         <v>16</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03382726746473013</v>
       </c>
@@ -8609,9 +8549,6 @@
       <c r="O55" t="n">
         <v>29</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.06131192227982336</v>
       </c>
@@ -8905,9 +8842,6 @@
       <c r="O57" t="n">
         <v>8</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -9201,9 +9135,6 @@
       <c r="O59" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -9497,9 +9428,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9721,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10014,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10307,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10600,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10893,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11186,6 @@
       <c r="O73" t="n">
         <v>5</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -11569,9 +11479,6 @@
       <c r="O75" t="n">
         <v>9</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -11865,9 +11772,6 @@
       <c r="O77" t="n">
         <v>25</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.05261589331879283</v>
       </c>
@@ -12161,9 +12065,6 @@
       <c r="O79" t="n">
         <v>29</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.06103443624979968</v>
       </c>
@@ -12457,9 +12358,6 @@
       <c r="O81" t="n">
         <v>11</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.02315099306026884</v>
       </c>
@@ -12753,9 +12651,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -13049,9 +12944,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13345,9 +13237,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13641,9 +13530,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -13937,9 +13823,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14116,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14529,9 +14409,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -14825,9 +14702,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -15121,9 +14995,6 @@
       <c r="O99" t="n">
         <v>8</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -15417,9 +15288,6 @@
       <c r="O101" t="n">
         <v>10</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.02096564599647205</v>
       </c>
@@ -15713,9 +15581,6 @@
       <c r="O103" t="n">
         <v>25</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.05241411499118011</v>
       </c>
@@ -16009,9 +15874,6 @@
       <c r="O105" t="n">
         <v>11</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.02306221059611925</v>
       </c>
@@ -16305,9 +16167,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -16600,9 +16459,6 @@
       </c>
       <c r="O109" t="n">
         <v>1</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0.002096564599647205</v>
